--- a/Documents/Requirement.xlsx
+++ b/Documents/Requirement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12180"/>
+    <workbookView windowWidth="27945" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Api List" sheetId="1" r:id="rId1"/>
@@ -551,7 +551,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,11 +571,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1046,152 +1053,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1210,6 +1217,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1678,19 +1694,19 @@
       </c>
     </row>
     <row r="9" ht="45" spans="1:5">
-      <c r="A9" s="5">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="9" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1763,19 +1779,19 @@
       </c>
     </row>
     <row r="14" ht="60" spans="1:5">
-      <c r="A14" s="5">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="9" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1814,19 +1830,19 @@
       </c>
     </row>
     <row r="17" ht="75" spans="1:5">
-      <c r="A17" s="5">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="9" t="s">
         <v>8</v>
       </c>
     </row>
